--- a/DATA/MASTER/C10_MASTER/Resultados_EDA/Analisis_Bivariado/correlacion_pearson.xlsx
+++ b/DATA/MASTER/C10_MASTER/Resultados_EDA/Analisis_Bivariado/correlacion_pearson.xlsx
@@ -642,35 +642,37 @@
         <v>-0.03855133467318509</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1363614358158486</v>
+        <v>0.05302571190612732</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1101415975106013</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+        <v>-0.14958013271134</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-0.1484692416938662</v>
+      </c>
       <c r="O2" t="n">
-        <v>0.06527344244900998</v>
+        <v>-0.1375544699528459</v>
       </c>
       <c r="P2" t="n">
         <v>0.1012240936052273</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.06527344244900998</v>
+        <v>0.08740001468002963</v>
       </c>
       <c r="R2" t="n">
-        <v>0.06527344244900998</v>
+        <v>-0.08026964631118289</v>
       </c>
       <c r="S2" t="n">
-        <v>0.06527344244900998</v>
+        <v>0.09090652604955818</v>
       </c>
       <c r="T2" t="n">
-        <v>0.06527344244900998</v>
+        <v>0.07523638501381925</v>
       </c>
       <c r="U2" t="n">
-        <v>0.06527344244900998</v>
+        <v>0.05490171626547605</v>
       </c>
       <c r="V2" t="n">
-        <v>0.06527344244900998</v>
+        <v>-0.1491805023370355</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
@@ -750,35 +752,37 @@
         <v>0.07572001857998817</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.08431672051741639</v>
+        <v>-0.01778843880673666</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.07950600098085515</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
+        <v>0.2229483529241251</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.742010982005294</v>
+      </c>
       <c r="O3" t="n">
-        <v>-0.1099427942928761</v>
+        <v>0.7803979883098209</v>
       </c>
       <c r="P3" t="n">
         <v>-0.0181756077518956</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1099427942928761</v>
+        <v>0.5620644277437404</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.1099427942928761</v>
+        <v>0.2983554071240889</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1099427942928761</v>
+        <v>0.515434645808221</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1099427942928761</v>
+        <v>0.6464144385323348</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1099427942928761</v>
+        <v>0.02729644442160151</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1099427942928761</v>
+        <v>-0.1763138976457927</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
@@ -858,35 +862,37 @@
         <v>0.02686422214390575</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03667409509603231</v>
+        <v>-0.02095079859119617</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02084280310586926</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
+        <v>-0.04987748473216388</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.4549187911361396</v>
+      </c>
       <c r="O4" t="n">
-        <v>-0.03711744993759238</v>
+        <v>0.5217972859808142</v>
       </c>
       <c r="P4" t="n">
         <v>0.1068019631369746</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.03711744993759238</v>
+        <v>0.6592220128201636</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.03711744993759238</v>
+        <v>0.2810356290728263</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.03711744993759238</v>
+        <v>0.6083160900901904</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.03711744993759238</v>
+        <v>0.7539169551178727</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.03711744993759238</v>
+        <v>-0.01622737855711299</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.03711744993759238</v>
+        <v>-0.3248649429406845</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
@@ -966,35 +972,37 @@
         <v>0.07270732474520589</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.02198695503487283</v>
+        <v>-0.009226852546206501</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.02448452289766701</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
+        <v>0.1090136244807524</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.6844731374453293</v>
+      </c>
       <c r="O5" t="n">
-        <v>-0.06649997879521374</v>
+        <v>0.7403711360407792</v>
       </c>
       <c r="P5" t="n">
         <v>0.03272189098643361</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.06649997879521374</v>
+        <v>0.6756635653196253</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.06649997879521374</v>
+        <v>0.309413270395233</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.06649997879521374</v>
+        <v>0.6245036593863702</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.06649997879521374</v>
+        <v>0.7692973879866617</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.06649997879521374</v>
+        <v>0.02207219471900676</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.06649997879521374</v>
+        <v>-0.2847089538253074</v>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
@@ -1074,35 +1082,37 @@
         <v>-0.06900551928004676</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1580694256695481</v>
+        <v>0.06635769075299695</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1462457652489939</v>
-      </c>
-      <c r="N6" t="inlineStr"/>
+        <v>-0.3832775452959649</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.6543879291716573</v>
+      </c>
       <c r="O6" t="n">
-        <v>0.1027990213387199</v>
+        <v>-0.6528293980413924</v>
       </c>
       <c r="P6" t="n">
         <v>0.1975276324798376</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1027990213387199</v>
+        <v>-0.1807002557426046</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1027990213387199</v>
+        <v>-0.2107221379804917</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1027990213387199</v>
+        <v>-0.1563178729290033</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1027990213387199</v>
+        <v>-0.2336949449228006</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1027990213387199</v>
+        <v>0.01157601090472417</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1027990213387199</v>
+        <v>-0.1129617181416724</v>
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="n">
@@ -1182,35 +1192,37 @@
         <v>0.1670421697075618</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05823258830724935</v>
+        <v>0.06061847087897843</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0620151726850936</v>
-      </c>
-      <c r="N7" t="inlineStr"/>
+        <v>0.03194561988713329</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.06356478455302564</v>
+      </c>
       <c r="O7" t="n">
-        <v>-0.03426512047246501</v>
+        <v>0.03632679122586472</v>
       </c>
       <c r="P7" t="n">
         <v>0.4829265677792562</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.03426512047246501</v>
+        <v>0.1686347525306436</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.03426512047246501</v>
+        <v>-0.005249362207486295</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.03426512047246501</v>
+        <v>0.1734402438732235</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.03426512047246501</v>
+        <v>0.1477969494021675</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.03426512047246501</v>
+        <v>0.00614209624315045</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.03426512047246501</v>
+        <v>-0.244954349262751</v>
       </c>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="n">
@@ -1290,35 +1302,37 @@
         <v>0.08737009277710962</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1033344722664292</v>
+        <v>0.1496443860777007</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0747659461470835</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
+        <v>0.008033412142833681</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.1269018208332336</v>
+      </c>
       <c r="O8" t="n">
-        <v>-0.05308268357166147</v>
+        <v>0.1603919032443668</v>
       </c>
       <c r="P8" t="n">
         <v>-0.2085481362621982</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.05308268357166147</v>
+        <v>0.06869506862122783</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.05308268357166147</v>
+        <v>0.03003184979733635</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.05308268357166147</v>
+        <v>0.07071533588577025</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.05308268357166147</v>
+        <v>0.09430332155177272</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.05308268357166147</v>
+        <v>0.03475423770283916</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.05308268357166147</v>
+        <v>0.07753995051801353</v>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="n">
@@ -1398,33 +1412,35 @@
         <v>-0.2775895191376329</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4767312946227878</v>
+        <v>0.5738938907334586</v>
       </c>
       <c r="M9" t="n">
-        <v>0.499999999999992</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
+        <v>-0.05727042918024371</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.03737597801422406</v>
+      </c>
       <c r="O9" t="n">
-        <v>-0.5976143046672051</v>
+        <v>0.0317712005499611</v>
       </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="n">
-        <v>-0.5976143046672051</v>
+        <v>0.164077949329475</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.5976143046672051</v>
+        <v>-0.2286464287798257</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5976143046672051</v>
+        <v>0.2236067977501002</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5976143046672051</v>
+        <v>0.01120311938285958</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5976143046672051</v>
+        <v>0.6717776667909484</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5976143046672051</v>
+        <v>-0.4177904915657767</v>
       </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="n">
@@ -1504,35 +1520,37 @@
         <v>-0.08315597549364631</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04367131467411464</v>
+        <v>0.2003634333944879</v>
       </c>
       <c r="M10" t="n">
-        <v>-5.085139114395169e-18</v>
-      </c>
-      <c r="N10" t="inlineStr"/>
+        <v>-2.25044491488462e-16</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-6.658990248124117e-16</v>
+      </c>
       <c r="O10" t="n">
-        <v>-1.570125135925706e-17</v>
+        <v>-6.365176601028946e-16</v>
       </c>
       <c r="P10" t="n">
         <v>8.233470708115982e-18</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.570125135925706e-17</v>
+        <v>-6.130925152756133e-16</v>
       </c>
       <c r="R10" t="n">
-        <v>-1.570125135925706e-17</v>
+        <v>-2.7891897329513e-16</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.570125135925706e-17</v>
+        <v>2.867947443118434e-16</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.570125135925706e-17</v>
+        <v>-4.273972530345011e-16</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.570125135925706e-17</v>
+        <v>-1.500295750840708e-16</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.570125135925706e-17</v>
+        <v>2.344320997466423e-16</v>
       </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="n">
@@ -1612,35 +1630,37 @@
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1332610346841787</v>
+        <v>0.2803289609323202</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1485262287251893</v>
-      </c>
-      <c r="N11" t="inlineStr"/>
+        <v>0.006986909701189678</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-2.378328711027237e-05</v>
+      </c>
       <c r="O11" t="n">
-        <v>0.1621212068381967</v>
+        <v>-1.856887534739706e-05</v>
       </c>
       <c r="P11" t="n">
         <v>1.095866489784743e-16</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1621212068381967</v>
+        <v>-0.01262812315486751</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1621212068381967</v>
+        <v>-0.2013390608428578</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1621212068381967</v>
+        <v>0.03597195807077174</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1621212068381967</v>
+        <v>0.001802262474808338</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1621212068381967</v>
+        <v>0.03842076008198912</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1621212068381967</v>
+        <v>-0.06596651424742957</v>
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="n">
@@ -1690,78 +1710,108 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1363614358158486</v>
+        <v>0.05302571190612732</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.08431672051741639</v>
+        <v>-0.01778843880673666</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03667409509603231</v>
+        <v>-0.02095079859119617</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.02198695503487283</v>
+        <v>-0.009226852546206501</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1580694256695481</v>
+        <v>0.06635769075299695</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05823258830724935</v>
+        <v>0.06061847087897843</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1033344722664292</v>
+        <v>0.1496443860777007</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4767312946227878</v>
+        <v>0.5738938907334586</v>
       </c>
       <c r="J12" t="n">
-        <v>0.04367131467411464</v>
+        <v>0.2003634333944879</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1332610346841787</v>
+        <v>0.2803289609323202</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9534625892455924</v>
-      </c>
-      <c r="N12" t="inlineStr"/>
+        <v>-0.1247170069727221</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.0270227191296991</v>
+      </c>
       <c r="O12" t="n">
-        <v>0.2279211529192758</v>
-      </c>
-      <c r="P12" t="inlineStr"/>
+        <v>0.02298387163221506</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4.700133484990419e-16</v>
+      </c>
       <c r="Q12" t="n">
-        <v>0.2279211529192758</v>
+        <v>0.06351851212363704</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2279211529192758</v>
+        <v>-0.4853104206730914</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2279211529192758</v>
+        <v>0.2069427325071138</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2279211529192758</v>
+        <v>0.009381082837646944</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2279211529192758</v>
+        <v>0.5321854724330795</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2279211529192758</v>
+        <v>-0.3094799228468937</v>
       </c>
       <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
+      <c r="X12" t="n">
+        <v>0.03714725886567891</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-1.124287996207211e-15</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.3054688065761905</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.07744231110813278</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0.3197639868668382</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-0.2991787543025804</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0.006288852928134508</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-0.1193262841718764</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.0696637698182548</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.02770773271092937</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-0.1338601117518703</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.323852901792617</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>-0.2456508470794034</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1770,78 +1820,108 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1101415975106013</v>
+        <v>-0.14958013271134</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.07950600098085515</v>
+        <v>0.2229483529241251</v>
       </c>
       <c r="D13" t="n">
-        <v>0.02084280310586926</v>
+        <v>-0.04987748473216388</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.02448452289766701</v>
+        <v>0.1090136244807524</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1462457652489939</v>
+        <v>-0.3832775452959649</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0620151726850936</v>
+        <v>0.03194561988713329</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0747659461470835</v>
+        <v>0.008033412142833681</v>
       </c>
       <c r="I13" t="n">
-        <v>0.499999999999992</v>
+        <v>-0.05727042918024371</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.085139114395169e-18</v>
+        <v>-2.25044491488462e-16</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1485262287251893</v>
+        <v>0.006986909701189678</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9534625892455924</v>
+        <v>-0.1247170069727221</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>0.5062751976952371</v>
+      </c>
       <c r="O13" t="n">
-        <v>0.2390457218668786</v>
-      </c>
-      <c r="P13" t="inlineStr"/>
+        <v>0.475304089113817</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.3201705596678281</v>
+      </c>
       <c r="Q13" t="n">
-        <v>0.2390457218668786</v>
+        <v>-0.1239567775673242</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2390457218668786</v>
+        <v>0.0731538480259263</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2390457218668786</v>
+        <v>-0.1760832875277166</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2390457218668786</v>
+        <v>-0.1037822336830228</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2390457218668786</v>
+        <v>0.07710360149752681</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2390457218668786</v>
+        <v>0.240432842618805</v>
       </c>
       <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
+      <c r="X13" t="n">
+        <v>0.4763078142886998</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.1137418246945865</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.06154075713416284</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.2709847944800031</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.3401991051269506</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.4033566098825888</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.2286938310486931</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.3572619781210574</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.07077663895302162</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.01870219358323334</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-0.1309859987347833</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-0.1155654960511252</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.2931316135503892</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1849,41 +1929,109 @@
           <t>POBLACION TOTAL</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+      <c r="B14" t="n">
+        <v>-0.1484692416938662</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.742010982005294</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.4549187911361396</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.6844731374453293</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.6543879291716573</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.06356478455302564</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1269018208332336</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.03737597801422406</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-6.658990248124117e-16</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-2.378328711027237e-05</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0270227191296991</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.5062751976952371</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.9958285597370201</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.09023988403398318</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.4107526984376335</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.258211751020801</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.378462298396867</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.4789269023948082</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.1459735862063124</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-0.1086025069730326</v>
+      </c>
       <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
+      <c r="X14" t="n">
+        <v>0.08318082935432386</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.1655307866515933</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.8267638495159672</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.8619537926675054</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-0.3838256452383184</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.5799106521258719</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8818171731579585</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.7497102795315989</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.8659236844879361</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.4205635342628807</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.5544804942160322</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.4872106816250005</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.03189797890002248</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1892,97 +2040,107 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06527344244900998</v>
+        <v>-0.1375544699528459</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.1099427942928761</v>
+        <v>0.7803979883098209</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.03711744993759238</v>
+        <v>0.5217972859808142</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.06649997879521374</v>
+        <v>0.7403711360407792</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1027990213387199</v>
+        <v>-0.6528293980413924</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.03426512047246501</v>
+        <v>0.03632679122586472</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.05308268357166147</v>
+        <v>0.1603919032443668</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5976143046672051</v>
+        <v>0.0317712005499611</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.570125135925706e-17</v>
+        <v>-6.365176601028946e-16</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1621212068381967</v>
+        <v>-1.856887534739706e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2279211529192758</v>
+        <v>0.02298387163221506</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2390457218668786</v>
-      </c>
-      <c r="N15" t="inlineStr"/>
+        <v>0.475304089113817</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.9958285597370201</v>
+      </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
-      <c r="P15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>-0.09183064255474163</v>
+      </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0.4510964194119269</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0.2745927394075916</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>0.4147515533761414</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>0.5281133927465498</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0.1309851995420934</v>
       </c>
       <c r="V15" t="n">
-        <v>1</v>
+        <v>-0.1255836487891999</v>
       </c>
       <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
+      <c r="X15" t="n">
+        <v>0.06345386824715546</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.2219856061591274</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.7040999979488151</v>
+      </c>
       <c r="AA15" t="n">
-        <v>-0.3070864805356978</v>
+        <v>0.8414613402522286</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.01241790347546931</v>
+        <v>-0.3810654038611623</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.0671354092828894</v>
+        <v>0.5535673411786384</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.3333028854830344</v>
+        <v>0.867321880399887</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.2325600442419217</v>
+        <v>0.7362901208741066</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.4406323819762324</v>
+        <v>-0.8876789949778077</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.05523024194740583</v>
+        <v>0.4344263608345776</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0.006797011851544715</v>
+        <v>0.6075522466993226</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0.2635128105986094</v>
+        <v>0.4815780329346122</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.2582666315817909</v>
+        <v>-0.01209515142829965</v>
       </c>
     </row>
     <row r="16">
@@ -2019,19 +2177,37 @@
       <c r="K16" t="n">
         <v>1.095866489784743e-16</v>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>4.700133484990419e-16</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.3201705596678281</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0.09023988403398318</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-0.09183064255474163</v>
+      </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
+      <c r="Q16" t="n">
+        <v>0.150962185581801</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.5806525903946</v>
+      </c>
       <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
+      <c r="T16" t="n">
+        <v>0.6443379523259972</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.912515249835361</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.6443379523259973</v>
+      </c>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="n">
         <v>0.9120738620329274</v>
@@ -2076,97 +2252,107 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.06527344244900998</v>
+        <v>0.08740001468002963</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.1099427942928761</v>
+        <v>0.5620644277437404</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.03711744993759238</v>
+        <v>0.6592220128201636</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.06649997879521374</v>
+        <v>0.6756635653196253</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1027990213387199</v>
+        <v>-0.1807002557426046</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.03426512047246501</v>
+        <v>0.1686347525306436</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.05308268357166147</v>
+        <v>0.06869506862122783</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5976143046672051</v>
+        <v>0.164077949329475</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.570125135925706e-17</v>
+        <v>-6.130925152756133e-16</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1621212068381967</v>
+        <v>-0.01262812315486751</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2279211529192758</v>
+        <v>0.06351851212363704</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2390457218668786</v>
-      </c>
-      <c r="N17" t="inlineStr"/>
+        <v>-0.1239567775673242</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.4107526984376335</v>
+      </c>
       <c r="O17" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
+        <v>0.4510964194119269</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.150962185581801</v>
+      </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0.292878705881763</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>0.9386140912483517</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>0.8827679829119515</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0.04344159385402684</v>
       </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>-0.4961504398114843</v>
       </c>
       <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+      <c r="X17" t="n">
+        <v>0.1037029891972125</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.6363793433471466</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.1787856773637478</v>
+      </c>
       <c r="AA17" t="n">
-        <v>-0.3070864805356978</v>
+        <v>0.3893483265859481</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.01241790347546931</v>
+        <v>-0.3827118775408581</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.0671354092828894</v>
+        <v>0.1655439399818396</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0.3333028854830344</v>
+        <v>0.4591343236657352</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.2325600442419217</v>
+        <v>0.3760924832481719</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.4406323819762324</v>
+        <v>-0.7158818882870452</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0.05523024194740583</v>
+        <v>0.3793708435523511</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0.006797011851544715</v>
+        <v>0.67686053414027</v>
       </c>
       <c r="AI17" t="n">
-        <v>-0.2635128105986094</v>
+        <v>0.4572892493953772</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.2582666315817909</v>
+        <v>-0.4313255377404301</v>
       </c>
     </row>
     <row r="18">
@@ -2176,97 +2362,107 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.06527344244900998</v>
+        <v>-0.08026964631118289</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.1099427942928761</v>
+        <v>0.2983554071240889</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.03711744993759238</v>
+        <v>0.2810356290728263</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.06649997879521374</v>
+        <v>0.309413270395233</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1027990213387199</v>
+        <v>-0.2107221379804917</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.03426512047246501</v>
+        <v>-0.005249362207486295</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.05308268357166147</v>
+        <v>0.03003184979733635</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5976143046672051</v>
+        <v>-0.2286464287798257</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.570125135925706e-17</v>
+        <v>-2.7891897329513e-16</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1621212068381967</v>
+        <v>-0.2013390608428578</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2279211529192758</v>
+        <v>-0.4853104206730914</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2390457218668786</v>
-      </c>
-      <c r="N18" t="inlineStr"/>
+        <v>0.0731538480259263</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.258211751020801</v>
+      </c>
       <c r="O18" t="n">
-        <v>1</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
+        <v>0.2745927394075916</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.5806525903946</v>
+      </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0.292878705881763</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>0.1254426416167134</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>0.2895349819677501</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>-0.3401488475278185</v>
       </c>
       <c r="V18" t="n">
-        <v>1</v>
+        <v>0.03974656302592157</v>
       </c>
       <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+      <c r="X18" t="n">
+        <v>-0.07391513943086508</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.02623580074598243</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.1686458777244479</v>
+      </c>
       <c r="AA18" t="n">
-        <v>-0.3070864805356978</v>
+        <v>0.2889848541967775</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.01241790347546931</v>
+        <v>-0.02504223850111718</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.0671354092828894</v>
+        <v>0.1982991925557253</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.3333028854830344</v>
+        <v>0.3092743736782185</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.2325600442419217</v>
+        <v>0.3898563228040449</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.4406323819762324</v>
+        <v>-0.3635071706862908</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.05523024194740583</v>
+        <v>0.08970971781523297</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0.006797011851544715</v>
+        <v>0.4330266797271836</v>
       </c>
       <c r="AI18" t="n">
-        <v>-0.2635128105986094</v>
+        <v>-0.08877170498542238</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.2582666315817909</v>
+        <v>-0.02753812150206941</v>
       </c>
     </row>
     <row r="19">
@@ -2276,97 +2472,101 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.06527344244900998</v>
+        <v>0.09090652604955818</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.1099427942928761</v>
+        <v>0.515434645808221</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.03711744993759238</v>
+        <v>0.6083160900901904</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.06649997879521374</v>
+        <v>0.6245036593863702</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1027990213387199</v>
+        <v>-0.1563178729290033</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.03426512047246501</v>
+        <v>0.1734402438732235</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.05308268357166147</v>
+        <v>0.07071533588577025</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5976143046672051</v>
+        <v>0.2236067977501002</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.570125135925706e-17</v>
+        <v>2.867947443118434e-16</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1621212068381967</v>
+        <v>0.03597195807077174</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2279211529192758</v>
+        <v>0.2069427325071138</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2390457218668786</v>
-      </c>
-      <c r="N19" t="inlineStr"/>
+        <v>-0.1760832875277166</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.378462298396867</v>
+      </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>0.4147515533761414</v>
       </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0.9386140912483517</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0.1254426416167134</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>0.815547154937789</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0.1208951797184169</v>
       </c>
       <c r="V19" t="n">
-        <v>1</v>
+        <v>-0.4367594950267238</v>
       </c>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+      <c r="Z19" t="n">
+        <v>0.1787856773637477</v>
+      </c>
       <c r="AA19" t="n">
-        <v>-0.3070864805356978</v>
+        <v>0.3398730715078331</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.01241790347546931</v>
+        <v>-0.3999673044235366</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.0671354092828894</v>
+        <v>0.1320762267397425</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.3333028854830344</v>
+        <v>0.4166409843276686</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.2325600442419217</v>
+        <v>0.2808555013342458</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.4406323819762324</v>
+        <v>-0.654525454133197</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0.05523024194740583</v>
+        <v>0.4220959149193472</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0.006797011851544715</v>
+        <v>0.5741610052634587</v>
       </c>
       <c r="AI19" t="n">
-        <v>-0.2635128105986094</v>
+        <v>0.4961478301777286</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.2582666315817909</v>
+        <v>-0.4651721919138456</v>
       </c>
     </row>
     <row r="20">
@@ -2376,97 +2576,107 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.06527344244900998</v>
+        <v>0.07523638501381925</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.1099427942928761</v>
+        <v>0.6464144385323348</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.03711744993759238</v>
+        <v>0.7539169551178727</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.06649997879521374</v>
+        <v>0.7692973879866617</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1027990213387199</v>
+        <v>-0.2336949449228006</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.03426512047246501</v>
+        <v>0.1477969494021675</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.05308268357166147</v>
+        <v>0.09430332155177272</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5976143046672051</v>
+        <v>0.01120311938285958</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.570125135925706e-17</v>
+        <v>-4.273972530345011e-16</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1621212068381967</v>
+        <v>0.001802262474808338</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2279211529192758</v>
+        <v>0.009381082837646944</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2390457218668786</v>
-      </c>
-      <c r="N20" t="inlineStr"/>
+        <v>-0.1037822336830228</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.4789269023948082</v>
+      </c>
       <c r="O20" t="n">
-        <v>1</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
+        <v>0.5281133927465498</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.6443379523259972</v>
+      </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0.8827679829119515</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0.2895349819677501</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>0.815547154937789</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>-0.08975286799197812</v>
       </c>
       <c r="V20" t="n">
-        <v>1</v>
+        <v>-0.6045802037767333</v>
       </c>
       <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
+      <c r="X20" t="n">
+        <v>0.4678107797451004</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.9518639659043954</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.1850003630571574</v>
+      </c>
       <c r="AA20" t="n">
-        <v>-0.3070864805356978</v>
+        <v>0.41976789551649</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.01241790347546931</v>
+        <v>-0.3786332360223205</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.0671354092828894</v>
+        <v>0.1905858393060969</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.3333028854830344</v>
+        <v>0.4880271344663334</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.2325600442419217</v>
+        <v>0.4340655285163475</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.4406323819762324</v>
+        <v>-0.7479876127113941</v>
       </c>
       <c r="AG20" t="n">
-        <v>-0.05523024194740583</v>
+        <v>0.3943420178519411</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.006797011851544715</v>
+        <v>0.7760656052800782</v>
       </c>
       <c r="AI20" t="n">
-        <v>-0.2635128105986094</v>
+        <v>0.4757218234477035</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.2582666315817909</v>
+        <v>-0.3263967639489032</v>
       </c>
     </row>
     <row r="21">
@@ -2476,97 +2686,107 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.06527344244900998</v>
+        <v>0.05490171626547605</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.1099427942928761</v>
+        <v>0.02729644442160151</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.03711744993759238</v>
+        <v>-0.01622737855711299</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.06649997879521374</v>
+        <v>0.02207219471900676</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1027990213387199</v>
+        <v>0.01157601090472417</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.03426512047246501</v>
+        <v>0.00614209624315045</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.05308268357166147</v>
+        <v>0.03475423770283916</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5976143046672051</v>
+        <v>0.6717776667909484</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.570125135925706e-17</v>
+        <v>-1.500295750840708e-16</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1621212068381967</v>
+        <v>0.03842076008198912</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2279211529192758</v>
+        <v>0.5321854724330795</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2390457218668786</v>
-      </c>
-      <c r="N21" t="inlineStr"/>
+        <v>0.07710360149752681</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.1459735862063124</v>
+      </c>
       <c r="O21" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
+        <v>0.1309851995420934</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.912515249835361</v>
+      </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0.04344159385402684</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>-0.3401488475278185</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>0.1208951797184169</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>-0.08975286799197812</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>-0.318579991192718</v>
       </c>
       <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
+      <c r="X21" t="n">
+        <v>-0.804659027853817</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-0.5045140684561116</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.06194078026209465</v>
+      </c>
       <c r="AA21" t="n">
-        <v>-0.3070864805356978</v>
+        <v>0.1861533338046287</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.01241790347546931</v>
+        <v>-0.1473133731912606</v>
       </c>
       <c r="AC21" t="n">
-        <v>-0.0671354092828894</v>
+        <v>0.01197893944463725</v>
       </c>
       <c r="AD21" t="n">
-        <v>-0.3333028854830344</v>
+        <v>0.2383044671788138</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.2325600442419217</v>
+        <v>-0.02761702380783805</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.4406323819762324</v>
+        <v>-0.1412579194290284</v>
       </c>
       <c r="AG21" t="n">
-        <v>-0.05523024194740583</v>
+        <v>0.1114591583125295</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.006797011851544715</v>
+        <v>-0.1988481235654808</v>
       </c>
       <c r="AI21" t="n">
-        <v>-0.2635128105986094</v>
+        <v>0.2278970014206812</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.2582666315817909</v>
+        <v>-0.2619498237560038</v>
       </c>
     </row>
     <row r="22">
@@ -2576,97 +2796,107 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.06527344244900998</v>
+        <v>-0.1491805023370355</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.1099427942928761</v>
+        <v>-0.1763138976457927</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.03711744993759238</v>
+        <v>-0.3248649429406845</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.06649997879521374</v>
+        <v>-0.2847089538253074</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1027990213387199</v>
+        <v>-0.1129617181416724</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.03426512047246501</v>
+        <v>-0.244954349262751</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.05308268357166147</v>
+        <v>0.07753995051801353</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5976143046672051</v>
+        <v>-0.4177904915657767</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.570125135925706e-17</v>
+        <v>2.344320997466423e-16</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1621212068381967</v>
+        <v>-0.06596651424742957</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2279211529192758</v>
+        <v>-0.3094799228468937</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2390457218668786</v>
-      </c>
-      <c r="N22" t="inlineStr"/>
+        <v>0.240432842618805</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.1086025069730326</v>
+      </c>
       <c r="O22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
+        <v>-0.1255836487891999</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-0.6443379523259973</v>
+      </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>-0.4961504398114843</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0.03974656302592157</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>-0.4367594950267238</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>-0.6045802037767333</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>-0.318579991192718</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
       <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
+      <c r="X22" t="n">
+        <v>-0.4678107797451004</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-0.9518639659043956</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-0.02287627111691448</v>
+      </c>
       <c r="AA22" t="n">
-        <v>-0.3070864805356978</v>
+        <v>-0.2396639719547481</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.01241790347546931</v>
+        <v>0.2883807128849212</v>
       </c>
       <c r="AC22" t="n">
-        <v>-0.0671354092828894</v>
+        <v>0.007615366226400961</v>
       </c>
       <c r="AD22" t="n">
-        <v>-0.3333028854830344</v>
+        <v>-0.2134906556722858</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.2325600442419217</v>
+        <v>-0.07748348147199803</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.4406323819762324</v>
+        <v>0.4431757510724208</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0.05523024194740583</v>
+        <v>-0.05380922323029452</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.006797011851544715</v>
+        <v>-0.2894904917069797</v>
       </c>
       <c r="AI22" t="n">
-        <v>-0.2635128105986094</v>
+        <v>-0.3841955629240749</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.2582666315817909</v>
+        <v>0.3319726517042957</v>
       </c>
     </row>
     <row r="23">
@@ -2747,19 +2977,37 @@
       <c r="K24" t="n">
         <v>0.01178488726948001</v>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>0.03714725886567891</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.4763078142886998</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.08318082935432386</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.06345386824715546</v>
+      </c>
       <c r="P24" t="n">
         <v>0.9120738620329274</v>
       </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
+      <c r="Q24" t="n">
+        <v>0.1037029891972125</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-0.07391513943086508</v>
+      </c>
       <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
+      <c r="T24" t="n">
+        <v>0.4678107797451004</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.804659027853817</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-0.4678107797451004</v>
+      </c>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="n">
         <v>1</v>
@@ -2835,19 +3083,37 @@
       <c r="K25" t="n">
         <v>-1.975893491357484e-16</v>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>-1.124287996207211e-15</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.1137418246945865</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.1655307866515933</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.2219856061591274</v>
+      </c>
       <c r="P25" t="n">
         <v>0.7290766549206337</v>
       </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
+      <c r="Q25" t="n">
+        <v>0.6363793433471466</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.02623580074598243</v>
+      </c>
       <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
+      <c r="T25" t="n">
+        <v>0.9518639659043954</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.5045140684561116</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.9518639659043956</v>
+      </c>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="n">
         <v>0.4738421726226397</v>
@@ -2923,17 +3189,37 @@
       <c r="K26" t="n">
         <v>-0.05161250452752385</v>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>0.3054688065761905</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.06154075713416284</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.8267638495159672</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.7040999979488151</v>
+      </c>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
+      <c r="Q26" t="n">
+        <v>0.1787856773637478</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.1686458777244479</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.1787856773637477</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.1850003630571574</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.06194078026209465</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-0.02287627111691448</v>
+      </c>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
@@ -3005,32 +3291,38 @@
       <c r="K27" t="n">
         <v>-0.2666707325613968</v>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>-0.07744231110813278</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.2709847944800031</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.8619537926675054</v>
+      </c>
       <c r="O27" t="n">
-        <v>-0.3070864805356978</v>
+        <v>0.8414613402522286</v>
       </c>
       <c r="P27" t="n">
         <v>0.6423207431509059</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.3070864805356978</v>
+        <v>0.3893483265859481</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.3070864805356978</v>
+        <v>0.2889848541967775</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.3070864805356978</v>
+        <v>0.3398730715078331</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.3070864805356978</v>
+        <v>0.41976789551649</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.3070864805356978</v>
+        <v>0.1861533338046287</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.3070864805356978</v>
+        <v>-0.2396639719547481</v>
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
@@ -3109,30 +3401,36 @@
       <c r="K28" t="n">
         <v>-0.01673788411917651</v>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>-0.3197639868668382</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.3401991051269506</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-0.3838256452383184</v>
+      </c>
       <c r="O28" t="n">
-        <v>0.01241790347546931</v>
+        <v>-0.3810654038611623</v>
       </c>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="n">
-        <v>0.01241790347546931</v>
+        <v>-0.3827118775408581</v>
       </c>
       <c r="R28" t="n">
-        <v>0.01241790347546931</v>
+        <v>-0.02504223850111718</v>
       </c>
       <c r="S28" t="n">
-        <v>0.01241790347546931</v>
+        <v>-0.3999673044235366</v>
       </c>
       <c r="T28" t="n">
-        <v>0.01241790347546931</v>
+        <v>-0.3786332360223205</v>
       </c>
       <c r="U28" t="n">
-        <v>0.01241790347546931</v>
+        <v>-0.1473133731912606</v>
       </c>
       <c r="V28" t="n">
-        <v>0.01241790347546931</v>
+        <v>0.2883807128849212</v>
       </c>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="n">
@@ -3211,32 +3509,38 @@
       <c r="K29" t="n">
         <v>-0.2378330783204312</v>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>-0.2991787543025804</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.4033566098825888</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.5799106521258719</v>
+      </c>
       <c r="O29" t="n">
-        <v>-0.0671354092828894</v>
+        <v>0.5535673411786384</v>
       </c>
       <c r="P29" t="n">
         <v>0.7984031019722234</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.0671354092828894</v>
+        <v>0.1655439399818396</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.0671354092828894</v>
+        <v>0.1982991925557253</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.0671354092828894</v>
+        <v>0.1320762267397425</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.0671354092828894</v>
+        <v>0.1905858393060969</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.0671354092828894</v>
+        <v>0.01197893944463725</v>
       </c>
       <c r="V29" t="n">
-        <v>-0.0671354092828894</v>
+        <v>0.007615366226400961</v>
       </c>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="n">
@@ -3315,32 +3619,38 @@
       <c r="K30" t="n">
         <v>-0.2963961843847241</v>
       </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>-0.006288852928134508</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.2286938310486931</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.8818171731579585</v>
+      </c>
       <c r="O30" t="n">
-        <v>-0.3333028854830344</v>
+        <v>0.867321880399887</v>
       </c>
       <c r="P30" t="n">
         <v>0.6749434914474639</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.3333028854830344</v>
+        <v>0.4591343236657352</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.3333028854830344</v>
+        <v>0.3092743736782185</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.3333028854830344</v>
+        <v>0.4166409843276686</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.3333028854830344</v>
+        <v>0.4880271344663334</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.3333028854830344</v>
+        <v>0.2383044671788138</v>
       </c>
       <c r="V30" t="n">
-        <v>-0.3333028854830344</v>
+        <v>-0.2134906556722858</v>
       </c>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="n">
@@ -3419,32 +3729,38 @@
       <c r="K31" t="n">
         <v>-0.2016064021504923</v>
       </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>-0.1193262841718764</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.3572619781210574</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.7497102795315989</v>
+      </c>
       <c r="O31" t="n">
-        <v>0.2325600442419217</v>
+        <v>0.7362901208741066</v>
       </c>
       <c r="P31" t="n">
         <v>0.6109960344993463</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.2325600442419217</v>
+        <v>0.3760924832481719</v>
       </c>
       <c r="R31" t="n">
-        <v>0.2325600442419217</v>
+        <v>0.3898563228040449</v>
       </c>
       <c r="S31" t="n">
-        <v>0.2325600442419217</v>
+        <v>0.2808555013342458</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2325600442419217</v>
+        <v>0.4340655285163475</v>
       </c>
       <c r="U31" t="n">
-        <v>0.2325600442419217</v>
+        <v>-0.02761702380783805</v>
       </c>
       <c r="V31" t="n">
-        <v>0.2325600442419217</v>
+        <v>-0.07748348147199803</v>
       </c>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="n">
@@ -3521,32 +3837,38 @@
       <c r="K32" t="n">
         <v>0.3289291172526014</v>
       </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>0.0696637698182548</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-0.07077663895302162</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-0.8659236844879361</v>
+      </c>
       <c r="O32" t="n">
-        <v>0.4406323819762324</v>
+        <v>-0.8876789949778077</v>
       </c>
       <c r="P32" t="n">
         <v>-0.9946976878214308</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.4406323819762324</v>
+        <v>-0.7158818882870452</v>
       </c>
       <c r="R32" t="n">
-        <v>0.4406323819762324</v>
+        <v>-0.3635071706862908</v>
       </c>
       <c r="S32" t="n">
-        <v>0.4406323819762324</v>
+        <v>-0.654525454133197</v>
       </c>
       <c r="T32" t="n">
-        <v>0.4406323819762324</v>
+        <v>-0.7479876127113941</v>
       </c>
       <c r="U32" t="n">
-        <v>0.4406323819762324</v>
+        <v>-0.1412579194290284</v>
       </c>
       <c r="V32" t="n">
-        <v>0.4406323819762324</v>
+        <v>0.4431757510724208</v>
       </c>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="n">
@@ -3625,32 +3947,38 @@
       <c r="K33" t="n">
         <v>-0.02947936404403558</v>
       </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>0.02770773271092937</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.01870219358323334</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.4205635342628807</v>
+      </c>
       <c r="O33" t="n">
-        <v>-0.05523024194740583</v>
+        <v>0.4344263608345776</v>
       </c>
       <c r="P33" t="n">
         <v>0.9326897814624298</v>
       </c>
       <c r="Q33" t="n">
-        <v>-0.05523024194740583</v>
+        <v>0.3793708435523511</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.05523024194740583</v>
+        <v>0.08970971781523297</v>
       </c>
       <c r="S33" t="n">
-        <v>-0.05523024194740583</v>
+        <v>0.4220959149193472</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.05523024194740583</v>
+        <v>0.3943420178519411</v>
       </c>
       <c r="U33" t="n">
-        <v>-0.05523024194740583</v>
+        <v>0.1114591583125295</v>
       </c>
       <c r="V33" t="n">
-        <v>-0.05523024194740583</v>
+        <v>-0.05380922323029452</v>
       </c>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="n">
@@ -3729,32 +4057,38 @@
       <c r="K34" t="n">
         <v>-0.1016810236171298</v>
       </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>-0.1338601117518703</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-0.1309859987347833</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.5544804942160322</v>
+      </c>
       <c r="O34" t="n">
-        <v>-0.006797011851544715</v>
+        <v>0.6075522466993226</v>
       </c>
       <c r="P34" t="n">
         <v>0.9256959649302327</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0.006797011851544715</v>
+        <v>0.67686053414027</v>
       </c>
       <c r="R34" t="n">
-        <v>-0.006797011851544715</v>
+        <v>0.4330266797271836</v>
       </c>
       <c r="S34" t="n">
-        <v>-0.006797011851544715</v>
+        <v>0.5741610052634587</v>
       </c>
       <c r="T34" t="n">
-        <v>-0.006797011851544715</v>
+        <v>0.7760656052800782</v>
       </c>
       <c r="U34" t="n">
-        <v>-0.006797011851544715</v>
+        <v>-0.1988481235654808</v>
       </c>
       <c r="V34" t="n">
-        <v>-0.006797011851544715</v>
+        <v>-0.2894904917069797</v>
       </c>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="n">
@@ -3833,32 +4167,38 @@
       <c r="K35" t="n">
         <v>-0.08287207166646829</v>
       </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>0.323852901792617</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-0.1155654960511252</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.4872106816250005</v>
+      </c>
       <c r="O35" t="n">
-        <v>-0.2635128105986094</v>
+        <v>0.4815780329346122</v>
       </c>
       <c r="P35" t="n">
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.2635128105986094</v>
+        <v>0.4572892493953772</v>
       </c>
       <c r="R35" t="n">
-        <v>-0.2635128105986094</v>
+        <v>-0.08877170498542238</v>
       </c>
       <c r="S35" t="n">
-        <v>-0.2635128105986094</v>
+        <v>0.4961478301777286</v>
       </c>
       <c r="T35" t="n">
-        <v>-0.2635128105986094</v>
+        <v>0.4757218234477035</v>
       </c>
       <c r="U35" t="n">
-        <v>-0.2635128105986094</v>
+        <v>0.2278970014206812</v>
       </c>
       <c r="V35" t="n">
-        <v>-0.2635128105986094</v>
+        <v>-0.3841955629240749</v>
       </c>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="n">
@@ -3937,32 +4277,38 @@
       <c r="K36" t="n">
         <v>0.01261055012029162</v>
       </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>-0.2456508470794034</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.2931316135503892</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.03189797890002248</v>
+      </c>
       <c r="O36" t="n">
-        <v>0.2582666315817909</v>
+        <v>-0.01209515142829965</v>
       </c>
       <c r="P36" t="n">
         <v>0.1652778465405537</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.2582666315817909</v>
+        <v>-0.4313255377404301</v>
       </c>
       <c r="R36" t="n">
-        <v>0.2582666315817909</v>
+        <v>-0.02753812150206941</v>
       </c>
       <c r="S36" t="n">
-        <v>0.2582666315817909</v>
+        <v>-0.4651721919138456</v>
       </c>
       <c r="T36" t="n">
-        <v>0.2582666315817909</v>
+        <v>-0.3263967639489032</v>
       </c>
       <c r="U36" t="n">
-        <v>0.2582666315817909</v>
+        <v>-0.2619498237560038</v>
       </c>
       <c r="V36" t="n">
-        <v>0.2582666315817909</v>
+        <v>0.3319726517042957</v>
       </c>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="n">
